--- a/content/post/drafts/season-prediction/ladies_simple-model-tests-actual_mae.xlsx
+++ b/content/post/drafts/season-prediction/ladies_simple-model-tests-actual_mae.xlsx
@@ -610,25 +610,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.129371398716171</v>
+        <v>0.130173735251832</v>
       </c>
       <c r="C9" t="n">
-        <v>0.17503256413924</v>
+        <v>0.171487611915542</v>
       </c>
       <c r="D9" t="n">
-        <v>0.16583325471729</v>
+        <v>0.162576110616326</v>
       </c>
       <c r="E9" t="n">
-        <v>0.227826085400802</v>
+        <v>0.22603280112037</v>
       </c>
       <c r="F9" t="n">
-        <v>0.133217778199229</v>
+        <v>0.136063207251141</v>
       </c>
       <c r="G9" t="n">
-        <v>0.132033422315652</v>
+        <v>0.128208966037764</v>
       </c>
       <c r="H9" t="n">
-        <v>0.160552417248064</v>
+        <v>0.159090405365496</v>
       </c>
     </row>
     <row r="10">
